--- a/Shared/Templates/MachineInterfaces/TEMPLATE_INTERFACES_v0.0.xlsx
+++ b/Shared/Templates/MachineInterfaces/TEMPLATE_INTERFACES_v0.0.xlsx
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="&lt;GENERIC&gt;" sheetId="4" r:id="rId1"/>
     <sheet name="SORTER" sheetId="2" r:id="rId2"/>
-    <sheet name="FVT_GENERIC" sheetId="5" r:id="rId3"/>
+    <sheet name="FVTGENERIC" sheetId="5" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/Shared/Templates/MachineInterfaces/TEMPLATE_INTERFACES_v0.0.xlsx
+++ b/Shared/Templates/MachineInterfaces/TEMPLATE_INTERFACES_v0.0.xlsx
@@ -133,7 +133,7 @@
     <t>Expression Side 1</t>
   </si>
   <si>
-    <t>"Clock 1Hz"</t>
+    <t>"Clock_1Hz"</t>
   </si>
   <si>
     <t>AREA</t>
@@ -190,7 +190,7 @@
     <t>PNC_Q_SORTER-&lt;index&gt; SAFETY ENCODER FAILURE</t>
   </si>
   <si>
-    <t>PNC_I_SORTER-&lt;index&gt; SORTER- RUNNING</t>
+    <t>PNC_I_SORTER-&lt;index&gt; SORTER RUNNING</t>
   </si>
   <si>
     <t>PNC_I_SORTER-&lt;index&gt; EMERGENCY RESET</t>
